--- a/etf_holdings/2026-10-02_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.21%2510</t>
+          <t>-0.4%2500</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.90%11,464,000</t>
+          <t>9.79%11,464,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.90%</t>
+          <t>9.79%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.22%4980</t>
+          <t>+7.41%1305</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>+7.41%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4980</v>
+        <v>1305</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.71%5,086,000</t>
+          <t>8.96%20,100,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.71%</t>
+          <t>8.96%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5086000</v>
+        <v>20100000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+3.4%1215</t>
+          <t>-0.6%4950</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1215</v>
+        <v>4950</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.40%20,100,000</t>
+          <t>8.60%5,086,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.40%</t>
+          <t>8.60%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>20100000</v>
+        <v>5086000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.81%4975</t>
+          <t>+4.22%5185</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4975</v>
+        <v>5185</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.96%4,650,000</t>
+          <t>8.23%4,650,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.96%</t>
+          <t>8.23%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.18%3510</t>
+          <t>-1.99%3440</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3510</v>
+        <v>3440</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.11%5,889,000</t>
+          <t>6.92%5,889,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.11%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.1%6875</t>
+          <t>-1.09%6800</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6875</v>
+        <v>6800</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.92%2,502,000</t>
+          <t>5.81%2,502,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>5.81%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+9.85%602</t>
+          <t>+3.99%626</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>+3.99%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.13%24,757,000</t>
+          <t>5.29%24,757,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.13%</t>
+          <t>5.29%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.79%1905</t>
+          <t>0%161.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1905</v>
+        <v>161.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.84%7,389,000</t>
+          <t>4.80%87,118,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.84%</t>
+          <t>4.80%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7389000</v>
+        <v>87118000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+4.53%161.5</t>
+          <t>-1.05%1885</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>161.5</v>
+        <v>1885</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.84%87,118,000</t>
+          <t>4.76%7,389,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.84%</t>
+          <t>4.76%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>87118000</v>
+        <v>7389000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+5.97%1420</t>
+          <t>-1.85%5030</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+5.97%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1420</v>
+        <v>5030</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.37%8,937,000</t>
+          <t>4.53%2,499,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.37%</t>
+          <t>4.53%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8937000</v>
+        <v>2499000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.85%5030</t>
+          <t>+2.82%1460</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5030</v>
+        <v>1460</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.32%2,499,000</t>
+          <t>4.46%8,937,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.46%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2499000</v>
+        <v>8937000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+7.04%1900</t>
+          <t>+3.42%1965</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+7.04%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1900</v>
+        <v>1965</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.09%6,264,000</t>
+          <t>4.20%6,264,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.09%</t>
+          <t>4.20%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.54%2555</t>
+          <t>+0.99%1535</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2555</v>
+        <v>1535</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.41%3,876,848</t>
+          <t>3.40%6,151,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>3876848</v>
+        <v>6151000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.96%2110</t>
+          <t>-0.59%2540</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2110</v>
+        <v>2540</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.38%4,662,561</t>
+          <t>3.36%3,876,848</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>4662561</v>
+        <v>3876848</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:18</t>
+          <t>2026-10-02 19:04:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.99%1535</t>
+          <t>-1.18%2085</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1535</v>
+        <v>2085</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.25%6,151,000</t>
+          <t>3.07%4,315,561</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>6151000</v>
+        <v>4315561</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:25</t>
+          <t>2026-10-02 19:04:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,35 +1424,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1%710</t>
+          <t>+0.42%713</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>713</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.06%12,526,000</t>
+          <t>2.50%10,276,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>12526000</v>
+        <v>10276000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:25</t>
+          <t>2026-10-02 19:04:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1487,27 +1487,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.65%2390</t>
+          <t>-3.35%2310</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.38%1,673,000</t>
+          <t>1.32%1,673,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:25</t>
+          <t>2026-10-02 19:04:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1550,27 +1550,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.51%296</t>
+          <t>-0.17%295.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>295.5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.32%12,938,450</t>
+          <t>1.31%12,938,450</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:25</t>
+          <t>2026-10-02 19:04:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11%168,900</t>
+          <t>1.09%168,900</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:25</t>
+          <t>2026-10-02 19:04:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.74%7900</t>
+          <t>0%7900</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:25</t>
+          <t>2026-10-02 19:04:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,17 +1739,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.23%1095</t>
+          <t>+0.91%1105</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:25</t>
+          <t>2026-10-02 19:04:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1802,27 +1802,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.59%510</t>
+          <t>+10%561</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>561</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.61%3,483,000</t>
+          <t>0.67%3,483,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:25</t>
+          <t>2026-10-02 19:04:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:25</t>
+          <t>2026-10-02 19:04:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1928,35 +1928,35 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+1.08%845</t>
+          <t>-0.47%841</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>841</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.30%1,044,000</t>
+          <t>0.27%949,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1044000</v>
+        <v>949000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:25</t>
+          <t>2026-10-02 19:04:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,27 +1986,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.49%1565</t>
+          <t>-2.12%3000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.26%476,000</t>
+          <t>0.26%251,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>476000</v>
+        <v>251000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:25</t>
+          <t>2026-10-02 19:04:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2049,36 +2049,36 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.12%3000</t>
+          <t>-3.51%1510</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.26%251,000</t>
+          <t>0.25%476,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>251000</v>
+        <v>476000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:25</t>
+          <t>2026-10-02 19:04:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.69%216.5</t>
+          <t>+0.23%217</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>217</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:25</t>
+          <t>2026-10-02 19:04:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2180,27 +2180,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.7%5770</t>
+          <t>+5.2%6070</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>+5.2%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.18%93,000</t>
+          <t>0.19%93,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:25</t>
+          <t>2026-10-02 19:04:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2243,17 +2243,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+1.77%230.5</t>
+          <t>+1.74%234.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>230.5</t>
+          <t>234.5</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2306,16 +2306,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.36%84.3</t>
+          <t>+0.47%84.7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>84.3</v>
+        <v>84.7</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.29%174</t>
+          <t>0%174</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.05%121,000</t>
+          <t>0.06%121,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2489,16 +2489,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.88%224.5</t>
+          <t>+0.67%226</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>224.5</v>
+        <v>226</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2550,16 +2550,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.3%18.95</t>
+          <t>+0.26%19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>18.95</v>
+        <v>19</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2672,16 +2672,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.67%3765</t>
+          <t>+1.2%3810</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3765</v>
+        <v>3810</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2733,16 +2733,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.03%76.5</t>
+          <t>-1.05%75.7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>76.5</v>
+        <v>75.7</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2794,16 +2794,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.25%1185</t>
+          <t>-0.42%1180</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2855,16 +2855,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+4.37%6205</t>
+          <t>+1.37%6290</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+4.37%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6205</v>
+        <v>6290</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2916,16 +2916,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.15%334</t>
+          <t>-0.6%332</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,16 +3038,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0%519</t>
+          <t>+1.35%526</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.35%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3099,16 +3099,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.14%95.3</t>
+          <t>+3.67%98.8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>+3.67%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>95.3</v>
+        <v>98.8</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:26</t>
+          <t>2026-10-02 19:05:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3160,16 +3160,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2.58%2080</t>
+          <t>+5.29%2190</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2080</v>
+        <v>2190</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:27</t>
+          <t>2026-10-02 19:05:02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:27</t>
+          <t>2026-10-02 19:05:02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:27</t>
+          <t>2026-10-02 19:05:02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3343,16 +3343,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.87%115.5</t>
+          <t>+9.96%127</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>+9.96%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>115.5</v>
+        <v>127</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:27</t>
+          <t>2026-10-02 19:05:02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3404,16 +3404,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.99%254</t>
+          <t>-1.18%251</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:27</t>
+          <t>2026-10-02 19:05:02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:27</t>
+          <t>2026-10-02 19:05:02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3526,16 +3526,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+3.2%177.5</t>
+          <t>-1.69%174.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+3.2%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>177.5</v>
+        <v>174.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-02_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:58</t>
+          <t>2026-10-02 22:48:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:59</t>
+          <t>2026-10-02 22:48:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:59</t>
+          <t>2026-10-02 22:48:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:59</t>
+          <t>2026-10-02 22:48:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:59</t>
+          <t>2026-10-02 22:48:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:59</t>
+          <t>2026-10-02 22:48:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:59</t>
+          <t>2026-10-02 22:48:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:59</t>
+          <t>2026-10-02 22:48:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:59</t>
+          <t>2026-10-02 22:48:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:59</t>
+          <t>2026-10-02 22:48:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:59</t>
+          <t>2026-10-02 22:48:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:59</t>
+          <t>2026-10-02 22:48:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:59</t>
+          <t>2026-10-02 22:48:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:59</t>
+          <t>2026-10-02 22:48:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 19:04:59</t>
+          <t>2026-10-02 22:48:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:00</t>
+          <t>2026-10-02 22:48:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:02</t>
+          <t>2026-10-02 22:48:55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:02</t>
+          <t>2026-10-02 22:48:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:02</t>
+          <t>2026-10-02 22:48:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:02</t>
+          <t>2026-10-02 22:48:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:02</t>
+          <t>2026-10-02 22:48:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:02</t>
+          <t>2026-10-02 22:48:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-02_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:49</t>
+          <t>2026-10-02 22:58:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:52</t>
+          <t>2026-10-02 22:58:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:52</t>
+          <t>2026-10-02 22:58:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:52</t>
+          <t>2026-10-02 22:58:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:52</t>
+          <t>2026-10-02 22:58:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:52</t>
+          <t>2026-10-02 22:58:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:52</t>
+          <t>2026-10-02 22:58:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:52</t>
+          <t>2026-10-02 22:58:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:52</t>
+          <t>2026-10-02 22:58:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:52</t>
+          <t>2026-10-02 22:58:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:52</t>
+          <t>2026-10-02 22:58:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:52</t>
+          <t>2026-10-02 22:58:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:52</t>
+          <t>2026-10-02 22:58:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:52</t>
+          <t>2026-10-02 22:58:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:52</t>
+          <t>2026-10-02 22:58:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:54</t>
+          <t>2026-10-02 22:58:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:55</t>
+          <t>2026-10-02 22:58:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:55</t>
+          <t>2026-10-02 22:58:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:55</t>
+          <t>2026-10-02 22:58:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:55</t>
+          <t>2026-10-02 22:58:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:55</t>
+          <t>2026-10-02 22:58:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 22:48:55</t>
+          <t>2026-10-02 22:58:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-02_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:01</t>
+          <t>2026-10-02 23:47:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:02</t>
+          <t>2026-10-02 23:47:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:02</t>
+          <t>2026-10-02 23:47:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:02</t>
+          <t>2026-10-02 23:47:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:02</t>
+          <t>2026-10-02 23:47:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:02</t>
+          <t>2026-10-02 23:47:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:02</t>
+          <t>2026-10-02 23:47:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:02</t>
+          <t>2026-10-02 23:47:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:02</t>
+          <t>2026-10-02 23:47:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:02</t>
+          <t>2026-10-02 23:47:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:02</t>
+          <t>2026-10-02 23:47:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:02</t>
+          <t>2026-10-02 23:47:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:02</t>
+          <t>2026-10-02 23:47:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:02</t>
+          <t>2026-10-02 23:47:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:02</t>
+          <t>2026-10-02 23:47:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:04</t>
+          <t>2026-10-02 23:47:53</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:05</t>
+          <t>2026-10-02 23:47:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:05</t>
+          <t>2026-10-02 23:47:54</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:05</t>
+          <t>2026-10-02 23:47:54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:05</t>
+          <t>2026-10-02 23:47:54</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:05</t>
+          <t>2026-10-02 23:47:54</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:05</t>
+          <t>2026-10-02 23:47:54</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
